--- a/data-manipulation-scripts/sheets-cleanup/processed_sheets/PINHAO 09_02.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/processed_sheets/PINHAO 09_02.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:D18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -432,11 +432,6 @@
           <t>QUANTIDADE</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>PREÇO</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -457,11 +452,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -482,7 +472,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -503,11 +492,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -528,7 +512,6 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -549,7 +532,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -570,11 +552,6 @@
           <t>9</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -595,11 +572,6 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -620,7 +592,6 @@
           <t>9</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -641,7 +612,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -662,7 +632,6 @@
           <t>9</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -683,7 +652,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -704,7 +672,6 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -725,7 +692,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -746,7 +712,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -767,7 +732,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -784,7 +748,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -801,7 +764,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
